--- a/Packages/cn.etetet.statesync/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Base/__tables__.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -114,12 +114,28 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>WeaponConfig</t>
+  </si>
+  <si>
+    <t>ET.WeaponConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/Weapon.xlsx</t>
+  </si>
+  <si>
+    <t>武器战斗配置表</t>
+  </si>
+  <si>
+    <t>WeaponConfigCategory</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -169,21 +185,21 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -474,7 +490,7 @@
     <col min="12" max="12" width="47.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -509,7 +525,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
+    <row r="2" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -541,7 +557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1">
+    <row r="3" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -564,60 +580,86 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:12">
+    <row r="4">
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="B5" s="2"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6">
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7">
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8">
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9">
       <c r="B9" s="2"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10">
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11">
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12">
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13">
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14">
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15">
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16">
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17">
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18">
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19">
       <c r="B19" s="2"/>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20">
       <c r="B20" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>
--- a/Packages/cn.etetet.statesync/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Base/__tables__.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.wow/Luban/Config/Base/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05ET\MatchTest\ETGame\Packages\cn.etetet.statesync\Luban\Config\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4615EC-EECE-BB40-B4FD-CC447FBEB323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11891077-1283-4CF1-BF4A-F9BF9D6BA4BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30" yWindow="7770" windowWidth="28830" windowHeight="7830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -129,14 +129,82 @@
   </si>
   <si>
     <t>WeaponConfigCategory</t>
+  </si>
+  <si>
+    <t>HeroDisplayConfig</t>
+  </si>
+  <si>
+    <t>ET.HeroDisplayConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/HeroDisplay.xlsx</t>
+  </si>
+  <si>
+    <t>英雄大厅3D展示配置表</t>
+  </si>
+  <si>
+    <t>HeroDisplayConfigCategory</t>
+  </si>
+  <si>
+    <t>RogueCardConfig</t>
+  </si>
+  <si>
+    <t>ET.RogueCardConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/RogueCard.xlsx</t>
+  </si>
+  <si>
+    <t>肉鸽牌配置表</t>
+  </si>
+  <si>
+    <t>RogueCardConfigCategory</t>
+  </si>
+  <si>
+    <t>RogueLevelEntryConfig</t>
+  </si>
+  <si>
+    <t>ET.RogueLevelEntryConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/RogueLevelEntry.xlsx</t>
+  </si>
+  <si>
+    <t>RogueLevelNumericEntryConfig</t>
+  </si>
+  <si>
+    <t>ET.RogueLevelNumericEntryConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/RogueLevelNumericEntry.xlsx</t>
+  </si>
+  <si>
+    <t>RogueKillExpEntryConfig</t>
+  </si>
+  <si>
+    <t>ET.RogueKillExpEntryConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/RogueKillExpEntry.xlsx</t>
+  </si>
+  <si>
+    <t>RogueGlobalConfig</t>
+  </si>
+  <si>
+    <t>ET.RogueGlobalConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/RogueGlobalConfig.xlsx</t>
+  </si>
+  <si>
+    <t>one</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,21 +253,21 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -479,18 +547,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="41.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.33203125" customWidth="1"/>
-    <col min="5" max="5" width="58.33203125" customWidth="1"/>
-    <col min="6" max="6" width="129.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.875" customWidth="1"/>
+    <col min="3" max="3" width="41.375" customWidth="1"/>
+    <col min="4" max="4" width="26.375" customWidth="1"/>
+    <col min="5" max="5" width="58.375" customWidth="1"/>
+    <col min="6" max="6" width="129.625" customWidth="1"/>
     <col min="7" max="10" width="18" customWidth="1"/>
-    <col min="12" max="12" width="47.33203125" customWidth="1"/>
+    <col min="12" max="12" width="47.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -525,7 +593,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1">
+    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -557,7 +625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1">
+    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -580,86 +648,179 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="0" t="b">
+      <c r="E4" t="b">
         <v>1</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="0" t="s">
+      <c r="J4" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="0" t="s">
+      <c r="L4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B11" s="2"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B12" s="2"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B13" s="2"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B14" s="2"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15" s="2"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B16" s="2"/>
     </row>
-    <row r="17">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" s="2"/>
     </row>
-    <row r="18">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" s="2"/>
     </row>
-    <row r="19">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" s="2"/>
     </row>
-    <row r="20">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>
--- a/Packages/cn.etetet.statesync/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Base/__tables__.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.wow/Luban/Config/Base/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05ET\MatchTest\ETGame\Packages\cn.etetet.statesync\Luban\Config\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4615EC-EECE-BB40-B4FD-CC447FBEB323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1626EC8-0BD6-4C25-9223-90E63C51EFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30" yWindow="7770" windowWidth="28830" windowHeight="7830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>##var</t>
   </si>
@@ -114,12 +114,154 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>WeaponConfig</t>
+  </si>
+  <si>
+    <t>ET.WeaponConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/Weapon.xlsx</t>
+  </si>
+  <si>
+    <t>武器战斗配置表</t>
+  </si>
+  <si>
+    <t>WeaponConfigCategory</t>
+  </si>
+  <si>
+    <t>HeroDisplayConfig</t>
+  </si>
+  <si>
+    <t>ET.HeroDisplayConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/HeroDisplay.xlsx</t>
+  </si>
+  <si>
+    <t>英雄大厅3D展示配置表</t>
+  </si>
+  <si>
+    <t>HeroDisplayConfigCategory</t>
+  </si>
+  <si>
+    <t>RogueCardConfig</t>
+  </si>
+  <si>
+    <t>ET.RogueCardConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/RogueCard.xlsx</t>
+  </si>
+  <si>
+    <t>肉鸽牌配置表</t>
+  </si>
+  <si>
+    <t>RogueCardConfigCategory</t>
+  </si>
+  <si>
+    <t>RogueLevelEntryConfig</t>
+  </si>
+  <si>
+    <t>ET.RogueLevelEntryConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/RogueLevelEntry.xlsx</t>
+  </si>
+  <si>
+    <t>RogueLevelNumericEntryConfig</t>
+  </si>
+  <si>
+    <t>ET.RogueLevelNumericEntryConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/RogueLevelNumericEntry.xlsx</t>
+  </si>
+  <si>
+    <t>RogueKillExpEntryConfig</t>
+  </si>
+  <si>
+    <t>ET.RogueKillExpEntryConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/RogueKillExpEntry.xlsx</t>
+  </si>
+  <si>
+    <t>RogueGlobalConfig</t>
+  </si>
+  <si>
+    <t>ET.RogueGlobalConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/RogueGlobalConfig.xlsx</t>
+  </si>
+  <si>
+    <t>one</t>
+  </si>
+  <si>
+    <t>TagsConfig</t>
+  </si>
+  <si>
+    <t>ET.TagsConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/Tags.xlsx</t>
+  </si>
+  <si>
+    <t>肉鸽标签配置表</t>
+  </si>
+  <si>
+    <t>TagsConfigCategory</t>
+  </si>
+  <si>
+    <t>TacticalItemConfig</t>
+  </si>
+  <si>
+    <t>ET.TacticalItemConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/TacticalItemConfig.xlsx</t>
+  </si>
+  <si>
+    <t>战术道具配置表</t>
+  </si>
+  <si>
+    <t>TacticalItemConfigCategory</t>
+  </si>
+  <si>
+    <t>MinimapConstConfig</t>
+  </si>
+  <si>
+    <t>ET.MinimapConstConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/MinimapConstConfig.xlsx</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>NavmeshGuardConfig</t>
+  </si>
+  <si>
+    <t>ET.NavmeshGuardConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/NavmeshGuardConfig.xlsx</t>
+  </si>
+  <si>
+    <t>导航防穿墙参数配置</t>
+  </si>
+  <si>
+    <t>NavmeshGuardConfigCategory</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -169,21 +311,21 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -463,18 +605,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="41.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.33203125" customWidth="1"/>
-    <col min="5" max="5" width="58.33203125" customWidth="1"/>
-    <col min="6" max="6" width="129.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.875" customWidth="1"/>
+    <col min="3" max="3" width="41.375" customWidth="1"/>
+    <col min="4" max="4" width="26.375" customWidth="1"/>
+    <col min="5" max="5" width="58.375" customWidth="1"/>
+    <col min="6" max="6" width="129.625" customWidth="1"/>
     <col min="7" max="10" width="18" customWidth="1"/>
-    <col min="12" max="12" width="47.33203125" customWidth="1"/>
+    <col min="12" max="12" width="47.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -509,7 +651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
+    <row r="2" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -541,7 +683,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1">
+    <row r="3" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -564,60 +706,276 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="B5" s="2"/>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="B6" s="2"/>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16" spans="1:12">
+    <row r="4">
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" s="0" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="0" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="J12" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="0" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="J15" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="L15" s="0" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17">
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18">
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19">
       <c r="B19" s="2"/>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20">
       <c r="B20" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>
--- a/Packages/cn.etetet.statesync/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Base/__tables__.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>##var</t>
   </si>
@@ -239,6 +239,15 @@
     <t>../../../../cn.etetet.statesync/Luban/Config/Datas/MinimapConstConfig.xlsx</t>
   </si>
   <si>
+    <t>MonsterCorpseLootConfig</t>
+  </si>
+  <si>
+    <t>ET.MonsterCorpseLootConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/MonsterCorpseLootConfig.xlsx</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -255,6 +264,18 @@
   </si>
   <si>
     <t>NavmeshGuardConfigCategory</t>
+  </si>
+  <si>
+    <t>MatchRobotConfig</t>
+  </si>
+  <si>
+    <t>ET.MatchRobotConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.statesync/Luban/Config/Datas/MatchRobotConfig.xlsx</t>
+  </si>
+  <si>
+    <t>匹配机器人配置表</t>
   </si>
 </sst>
 </file>
@@ -914,46 +935,69 @@
         <v>68</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="0" t="s">
-        <v>68</v>
+      <c r="E14" s="0" t="b">
+        <v>1</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="0" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E15" s="0" t="b">
         <v>1</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H15" s="0" t="s">
         <v>54</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="J16" s="0" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="2"/>
